--- a/Planning_Proyecto.XLSX
+++ b/Planning_Proyecto.XLSX
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06ae8d044cc0a8d9/Documentos/GitHub/B-Aura/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ejgar\OneDrive\Documentos\GitHub\B-Aura\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_AD4D2F04E46CFB4ACB3E2072BD56EE5E683EDF2F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36196EC6-A526-4E7B-98DE-329006A807E4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2EA6B1-0238-4714-A47F-89A2E3DEC540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-1584" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,6 +124,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -152,10 +160,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,7 +542,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -546,7 +556,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -557,7 +567,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -568,8 +578,9 @@
         <v>7</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -590,7 +601,7 @@
         <v>9</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -600,14 +611,14 @@
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C9" s="2">
         <f>AVERAGE(C2:C8)</f>
-        <v>1.4285714285714287E-2</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
   </sheetData>
@@ -682,23 +693,23 @@
         <v>23</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>21</v>
@@ -709,7 +720,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>22</v>
@@ -721,7 +732,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G11" s="1">
         <f>AVERAGE(G5:G10)</f>
-        <v>0.33333333333333331</v>
+        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>
